--- a/sim/resources/sample/global.xlsx
+++ b/sim/resources/sample/global.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12975"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="globalConfig" sheetId="1" r:id="rId1"/>
@@ -341,7 +341,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="164">
   <si>
     <t>sid</t>
   </si>
@@ -823,7 +823,16 @@
     <t>免费旋转活动被推广用户的流水游戏范围</t>
   </si>
   <si>
-    <t>奖励：广告收益倍数</t>
+    <t>广告：奖励收益倍数(必随机一个倍数)</t>
+  </si>
+  <si>
+    <t>1.5_2000|2_2000|3_3000</t>
+  </si>
+  <si>
+    <t>广告：建筑每次升级看广告次数</t>
+  </si>
+  <si>
+    <t>游客在赌场中设备的交互时间（秒）</t>
   </si>
 </sst>
 </file>
@@ -1931,7 +1940,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W88"/>
+  <dimension ref="A1:W90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
@@ -3220,8 +3229,30 @@
       <c r="B88" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D88" s="8">
-        <v>2</v>
+      <c r="C88" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="8">
+        <v>136</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D89" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="8">
+        <v>200</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D90" s="8">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
